--- a/python/optimization_dataset.xlsx
+++ b/python/optimization_dataset.xlsx
@@ -1,34 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/natomanzolli/Documents/GitHub/EvTransitMatsim/python/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C04D350-B2BB-CB40-8E3E-3B86D11CCD9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2180" yWindow="1860" windowWidth="27100" windowHeight="18220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1385,8 +1366,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1449,21 +1430,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1501,7 +1474,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1535,7 +1508,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1570,10 +1542,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1746,15 +1717,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N143"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="25.6640625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1798,7 +1765,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>32</v>
       </c>
@@ -1818,10 +1785,10 @@
         <v>49</v>
       </c>
       <c r="G2">
-        <v>55.033333333333331</v>
+        <v>55.03333333333333</v>
       </c>
       <c r="H2">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I2">
         <v>21.91293381081789</v>
@@ -1839,10 +1806,10 @@
         <v>28</v>
       </c>
       <c r="N2">
-        <v>5.9726348969521794</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.972634896952179</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>33</v>
       </c>
@@ -1865,13 +1832,13 @@
         <v>96</v>
       </c>
       <c r="H3">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I3">
-        <v>21.808201525308441</v>
+        <v>21.80820152530844</v>
       </c>
       <c r="J3">
-        <v>1.0443166285894421</v>
+        <v>1.044316628589442</v>
       </c>
       <c r="K3" t="s">
         <v>308</v>
@@ -1883,10 +1850,10 @@
         <v>33</v>
       </c>
       <c r="N3">
-        <v>3.4075314883294432</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+        <v>3.407531488329443</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>40</v>
       </c>
@@ -1906,16 +1873,16 @@
         <v>51</v>
       </c>
       <c r="G4">
-        <v>18.133333333333329</v>
+        <v>18.13333333333333</v>
       </c>
       <c r="H4">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I4">
-        <v>9.1175858091242059</v>
+        <v>9.117585809124206</v>
       </c>
       <c r="J4">
-        <v>1.0915212863850381</v>
+        <v>0.4366085145540153</v>
       </c>
       <c r="K4" t="s">
         <v>309</v>
@@ -1927,10 +1894,10 @@
         <v>41</v>
       </c>
       <c r="N4">
-        <v>7.5421206141652446</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.542120614165245</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>44</v>
       </c>
@@ -1950,16 +1917,16 @@
         <v>54</v>
       </c>
       <c r="G5">
-        <v>17.350000000000001</v>
+        <v>17.35</v>
       </c>
       <c r="H5">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I5">
-        <v>10.208290331356929</v>
+        <v>10.20829033135693</v>
       </c>
       <c r="J5">
-        <v>1.2220961148645306</v>
+        <v>0.4888384459458122</v>
       </c>
       <c r="K5" t="s">
         <v>310</v>
@@ -1971,10 +1938,10 @@
         <v>49</v>
       </c>
       <c r="N5">
-        <v>8.8256112374843791</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+        <v>8.825611237484379</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>45</v>
       </c>
@@ -1994,16 +1961,16 @@
         <v>54</v>
       </c>
       <c r="G6">
-        <v>17.350000000000001</v>
+        <v>17.35</v>
       </c>
       <c r="H6">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I6">
-        <v>10.080041590290019</v>
+        <v>10.08004159029002</v>
       </c>
       <c r="J6">
-        <v>1.20674268318237</v>
+        <v>0.482697073272948</v>
       </c>
       <c r="K6" t="s">
         <v>311</v>
@@ -2015,10 +1982,10 @@
         <v>51</v>
       </c>
       <c r="N6">
-        <v>8.7147333633631252</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+        <v>8.714733363363125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>46</v>
       </c>
@@ -2038,16 +2005,16 @@
         <v>54</v>
       </c>
       <c r="G7">
-        <v>18.266666666666669</v>
+        <v>18.26666666666667</v>
       </c>
       <c r="H7">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I7">
-        <v>8.3062023261879787</v>
+        <v>8.306202326187979</v>
       </c>
       <c r="J7">
-        <v>0.99438566719954757</v>
+        <v>0.397754266879819</v>
       </c>
       <c r="K7" t="s">
         <v>312</v>
@@ -2059,10 +2026,10 @@
         <v>53</v>
       </c>
       <c r="N7">
-        <v>6.8207865817237057</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.820786581723706</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>49</v>
       </c>
@@ -2082,16 +2049,16 @@
         <v>56</v>
       </c>
       <c r="G8">
-        <v>16.416666666666671</v>
+        <v>16.41666666666667</v>
       </c>
       <c r="H8">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I8">
-        <v>9.8895346480547808</v>
+        <v>9.889534648054781</v>
       </c>
       <c r="J8">
-        <v>1.1839359460693735</v>
+        <v>0.4735743784277494</v>
       </c>
       <c r="K8" t="s">
         <v>313</v>
@@ -2103,10 +2070,10 @@
         <v>59</v>
       </c>
       <c r="N8">
-        <v>9.0361230286794942</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+        <v>9.036123028679494</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9">
         <v>50</v>
       </c>
@@ -2129,13 +2096,13 @@
         <v>16.8</v>
       </c>
       <c r="H9">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I9">
-        <v>9.5930423502263729</v>
+        <v>9.593042350226373</v>
       </c>
       <c r="J9">
-        <v>1.1484410616664149</v>
+        <v>0.459376424666566</v>
       </c>
       <c r="K9" t="s">
         <v>314</v>
@@ -2147,10 +2114,10 @@
         <v>61</v>
       </c>
       <c r="N9">
-        <v>8.5652163841306894</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+        <v>8.565216384130689</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10">
         <v>53</v>
       </c>
@@ -2173,13 +2140,13 @@
         <v>17.8</v>
       </c>
       <c r="H10">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I10">
-        <v>9.1728786548792964</v>
+        <v>9.172878654879296</v>
       </c>
       <c r="J10">
-        <v>1.0981407270341288</v>
+        <v>0.4392562908136515</v>
       </c>
       <c r="K10" t="s">
         <v>315</v>
@@ -2191,10 +2158,10 @@
         <v>67</v>
       </c>
       <c r="N10">
-        <v>7.7299539226510916</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.729953922651092</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>54</v>
       </c>
@@ -2214,16 +2181,16 @@
         <v>60</v>
       </c>
       <c r="G11">
-        <v>18.383333333333329</v>
+        <v>18.38333333333333</v>
       </c>
       <c r="H11">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I11">
-        <v>8.3835796977965753</v>
+        <v>8.383579697796575</v>
       </c>
       <c r="J11">
-        <v>1.0036489798750134</v>
+        <v>0.4014595919500054</v>
       </c>
       <c r="K11" t="s">
         <v>316</v>
@@ -2235,10 +2202,10 @@
         <v>69</v>
       </c>
       <c r="N11">
-        <v>6.8406361994713656</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.840636199471366</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12">
         <v>55</v>
       </c>
@@ -2258,16 +2225,16 @@
         <v>55</v>
       </c>
       <c r="G12">
-        <v>16.733333333333331</v>
+        <v>16.73333333333333</v>
       </c>
       <c r="H12">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I12">
-        <v>7.5871775972116842</v>
+        <v>7.587177597211684</v>
       </c>
       <c r="J12">
-        <v>0.90830687248949848</v>
+        <v>0.3633227489957994</v>
       </c>
       <c r="K12" t="s">
         <v>317</v>
@@ -2279,10 +2246,10 @@
         <v>71</v>
       </c>
       <c r="N12">
-        <v>6.8012548182176449</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.801254818217645</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13">
         <v>56</v>
       </c>
@@ -2302,16 +2269,16 @@
         <v>50</v>
       </c>
       <c r="G13">
-        <v>14.616666666666671</v>
+        <v>14.61666666666667</v>
       </c>
       <c r="H13">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I13">
-        <v>8.3760815696042048</v>
+        <v>8.376081569604205</v>
       </c>
       <c r="J13">
-        <v>1.0027513336448213</v>
+        <v>0.4011005334579285</v>
       </c>
       <c r="K13" t="s">
         <v>318</v>
@@ -2323,10 +2290,10 @@
         <v>73</v>
       </c>
       <c r="N13">
-        <v>8.5957507555801431</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+        <v>8.595750755580143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14">
         <v>57</v>
       </c>
@@ -2349,13 +2316,13 @@
         <v>13.55</v>
       </c>
       <c r="H14">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I14">
-        <v>7.7786443706514312</v>
+        <v>7.778644370651431</v>
       </c>
       <c r="J14">
-        <v>0.93122851679536323</v>
+        <v>0.3724914067181453</v>
       </c>
       <c r="K14" t="s">
         <v>319</v>
@@ -2367,10 +2334,10 @@
         <v>75</v>
       </c>
       <c r="N14">
-        <v>8.6110454287654203</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+        <v>8.61104542876542</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15">
         <v>58</v>
       </c>
@@ -2393,13 +2360,13 @@
         <v>13.55</v>
       </c>
       <c r="H15">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I15">
-        <v>8.6789773826060568</v>
+        <v>8.678977382606057</v>
       </c>
       <c r="J15">
-        <v>1.0390128215397381</v>
+        <v>0.4156051286158952</v>
       </c>
       <c r="K15" t="s">
         <v>320</v>
@@ -2411,10 +2378,10 @@
         <v>77</v>
       </c>
       <c r="N15">
-        <v>9.6077240397853014</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+        <v>9.607724039785301</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16">
         <v>59</v>
       </c>
@@ -2434,16 +2401,16 @@
         <v>47</v>
       </c>
       <c r="G16">
-        <v>13.383333333333329</v>
+        <v>13.38333333333333</v>
       </c>
       <c r="H16">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I16">
-        <v>8.0414096790723804</v>
+        <v>8.04140967907238</v>
       </c>
       <c r="J16">
-        <v>0.96268573951521708</v>
+        <v>0.3850742958060868</v>
       </c>
       <c r="K16" t="s">
         <v>321</v>
@@ -2455,10 +2422,10 @@
         <v>81</v>
       </c>
       <c r="N16">
-        <v>9.0127879342031658</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+        <v>9.012787934203166</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17">
         <v>60</v>
       </c>
@@ -2481,13 +2448,13 @@
         <v>12.7</v>
       </c>
       <c r="H17">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I17">
-        <v>8.3251868375403344</v>
+        <v>8.325186837540334</v>
       </c>
       <c r="J17">
-        <v>0.9966584177594574</v>
+        <v>0.398663367103783</v>
       </c>
       <c r="K17" t="s">
         <v>322</v>
@@ -2502,7 +2469,7 @@
         <v>9.832897839614569</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14">
       <c r="A18">
         <v>61</v>
       </c>
@@ -2522,16 +2489,16 @@
         <v>47</v>
       </c>
       <c r="G18">
-        <v>12.866666666666671</v>
+        <v>12.86666666666667</v>
       </c>
       <c r="H18">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I18">
-        <v>8.0049682114584169</v>
+        <v>8.004968211458417</v>
       </c>
       <c r="J18">
-        <v>0.95832311124491909</v>
+        <v>0.3833292444979676</v>
       </c>
       <c r="K18" t="s">
         <v>323</v>
@@ -2543,10 +2510,10 @@
         <v>89</v>
       </c>
       <c r="N18">
-        <v>9.3322168268297592</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+        <v>9.332216826829759</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19">
         <v>62</v>
       </c>
@@ -2566,16 +2533,16 @@
         <v>46</v>
       </c>
       <c r="G19">
-        <v>12.633333333333329</v>
+        <v>12.63333333333333</v>
       </c>
       <c r="H19">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I19">
         <v>8.323488738604107</v>
       </c>
       <c r="J19">
-        <v>0.99645512807575376</v>
+        <v>0.3985820512303015</v>
       </c>
       <c r="K19" t="s">
         <v>324</v>
@@ -2587,10 +2554,10 @@
         <v>93</v>
       </c>
       <c r="N19">
-        <v>9.8827702701104183</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+        <v>9.882770270110418</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20">
         <v>63</v>
       </c>
@@ -2610,16 +2577,16 @@
         <v>46</v>
       </c>
       <c r="G20">
-        <v>12.633333333333329</v>
+        <v>12.63333333333333</v>
       </c>
       <c r="H20">
-        <v>20882.748515423689</v>
+        <v>20882.74851542369</v>
       </c>
       <c r="I20">
         <v>8.323488738604107</v>
       </c>
       <c r="J20">
-        <v>0.99645512807575376</v>
+        <v>0.3985820512303015</v>
       </c>
       <c r="K20" t="s">
         <v>325</v>
@@ -2631,10 +2598,10 @@
         <v>95</v>
       </c>
       <c r="N20">
-        <v>9.8827702701104183</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+        <v>9.882770270110418</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21">
         <v>64</v>
       </c>
@@ -2654,16 +2621,16 @@
         <v>54</v>
       </c>
       <c r="G21">
-        <v>55.866666666666667</v>
+        <v>55.86666666666667</v>
       </c>
       <c r="H21">
-        <v>20791.190512378838</v>
+        <v>20791.19051237884</v>
       </c>
       <c r="I21">
-        <v>21.075254867072061</v>
+        <v>21.07525486707206</v>
       </c>
       <c r="J21">
-        <v>1.3177615447697104</v>
+        <v>1.013662726745931</v>
       </c>
       <c r="K21" t="s">
         <v>326</v>
@@ -2675,10 +2642,10 @@
         <v>29</v>
       </c>
       <c r="N21">
-        <v>5.6586304834024048</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.658630483402405</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22">
         <v>65</v>
       </c>
@@ -2701,13 +2668,13 @@
         <v>57.85</v>
       </c>
       <c r="H22">
-        <v>20791.190512378838</v>
+        <v>20791.19051237884</v>
       </c>
       <c r="I22">
         <v>21.7449788320335</v>
       </c>
       <c r="J22">
-        <v>1.359637028231395</v>
+        <v>1.045874637101073</v>
       </c>
       <c r="K22" t="s">
         <v>327</v>
@@ -2719,10 +2686,10 @@
         <v>32</v>
       </c>
       <c r="N22">
-        <v>5.6382831889455902</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.63828318894559</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23">
         <v>66</v>
       </c>
@@ -2745,13 +2712,13 @@
         <v>58.3</v>
       </c>
       <c r="H23">
-        <v>20791.190512378838</v>
+        <v>20791.19051237884</v>
       </c>
       <c r="I23">
-        <v>21.801954409956711</v>
+        <v>21.80195440995671</v>
       </c>
       <c r="J23">
-        <v>1.3631995106806842</v>
+        <v>1.048615008215911</v>
       </c>
       <c r="K23" t="s">
         <v>328</v>
@@ -2763,10 +2730,10 @@
         <v>33</v>
       </c>
       <c r="N23">
-        <v>5.6094222324073861</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.609422232407386</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24">
         <v>67</v>
       </c>
@@ -2789,13 +2756,13 @@
         <v>59.1</v>
       </c>
       <c r="H24">
-        <v>20791.190512378838</v>
+        <v>20791.19051237884</v>
       </c>
       <c r="I24">
         <v>21.78419430362236</v>
       </c>
       <c r="J24">
-        <v>1.3620890337110798</v>
+        <v>1.047760795162369</v>
       </c>
       <c r="K24" t="s">
         <v>329</v>
@@ -2807,10 +2774,10 @@
         <v>35</v>
       </c>
       <c r="N24">
-        <v>5.5289833257924768</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.528983325792477</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25">
         <v>68</v>
       </c>
@@ -2833,13 +2800,13 @@
         <v>55.81666666666667</v>
       </c>
       <c r="H25">
-        <v>20791.190512378838</v>
+        <v>20791.19051237884</v>
       </c>
       <c r="I25">
-        <v>21.774078135799218</v>
+        <v>21.77407813579922</v>
       </c>
       <c r="J25">
-        <v>1.3614565053254517</v>
+        <v>1.047274234865732</v>
       </c>
       <c r="K25" t="s">
         <v>330</v>
@@ -2851,10 +2818,10 @@
         <v>37</v>
       </c>
       <c r="N25">
-        <v>5.8514990511254981</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.851499051125498</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26">
         <v>74</v>
       </c>
@@ -2877,13 +2844,13 @@
         <v>5.3</v>
       </c>
       <c r="H26">
-        <v>20791.190512378838</v>
+        <v>20791.19051237884</v>
       </c>
       <c r="I26">
         <v>1.962049213617963</v>
       </c>
       <c r="J26">
-        <v>1.1324310913988966</v>
+        <v>0.09436925761657472</v>
       </c>
       <c r="K26" t="s">
         <v>331</v>
@@ -2895,10 +2862,10 @@
         <v>50</v>
       </c>
       <c r="N26">
-        <v>5.5529694725036691</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.552969472503669</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27">
         <v>75</v>
       </c>
@@ -2918,16 +2885,16 @@
         <v>53</v>
       </c>
       <c r="G27">
-        <v>3.2833333333333332</v>
+        <v>3.283333333333333</v>
       </c>
       <c r="H27">
-        <v>20791.190512378838</v>
+        <v>20791.19051237884</v>
       </c>
       <c r="I27">
-        <v>2.0705205802670359</v>
+        <v>2.070520580267036</v>
       </c>
       <c r="J27">
-        <v>1.1950372417784956</v>
+        <v>0.09958643681487464</v>
       </c>
       <c r="K27" t="s">
         <v>332</v>
@@ -2939,10 +2906,10 @@
         <v>52</v>
       </c>
       <c r="N27">
-        <v>9.4592310773620945</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+        <v>9.459231077362094</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28">
         <v>76</v>
       </c>
@@ -2965,13 +2932,13 @@
         <v>2.833333333333333</v>
       </c>
       <c r="H28">
-        <v>20791.190512378838</v>
+        <v>20791.19051237884</v>
       </c>
       <c r="I28">
-        <v>1.4969643180301171</v>
+        <v>1.496964318030117</v>
       </c>
       <c r="J28">
-        <v>0.86399919262276459</v>
+        <v>0.07199993271856371</v>
       </c>
       <c r="K28" t="s">
         <v>333</v>
@@ -2983,10 +2950,10 @@
         <v>54</v>
       </c>
       <c r="N28">
-        <v>7.9251052131006183</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.925105213100618</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29">
         <v>77</v>
       </c>
@@ -3009,13 +2976,13 @@
         <v>2.166666666666667</v>
       </c>
       <c r="H29">
-        <v>20791.190512378838</v>
+        <v>20791.19051237884</v>
       </c>
       <c r="I29">
-        <v>1.3392847675333539</v>
+        <v>1.339284767533354</v>
       </c>
       <c r="J29">
-        <v>0.77299167649065148</v>
+        <v>0.06441597304088763</v>
       </c>
       <c r="K29" t="s">
         <v>334</v>
@@ -3030,7 +2997,7 @@
         <v>9.271971467538604</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14">
       <c r="A30">
         <v>78</v>
       </c>
@@ -3050,16 +3017,16 @@
         <v>54</v>
       </c>
       <c r="G30">
-        <v>1.9333333333333329</v>
+        <v>1.933333333333333</v>
       </c>
       <c r="H30">
-        <v>20791.190512378838</v>
+        <v>20791.19051237884</v>
       </c>
       <c r="I30">
         <v>1.375311245233767</v>
       </c>
       <c r="J30">
-        <v>0.79378498951173859</v>
+        <v>0.06614874912597822</v>
       </c>
       <c r="K30" t="s">
         <v>335</v>
@@ -3071,10 +3038,10 @@
         <v>58</v>
       </c>
       <c r="N30">
-        <v>10.670518281986119</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+        <v>10.67051828198612</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31">
         <v>79</v>
       </c>
@@ -3097,13 +3064,13 @@
         <v>1.25</v>
       </c>
       <c r="H31">
-        <v>20791.190512378838</v>
+        <v>20791.19051237884</v>
       </c>
       <c r="I31">
-        <v>0.90277487566038805</v>
+        <v>0.9027748756603881</v>
       </c>
       <c r="J31">
-        <v>0.86842056987827232</v>
+        <v>0.04342102849391362</v>
       </c>
       <c r="K31" t="s">
         <v>336</v>
@@ -3118,7 +3085,7 @@
         <v>10.83329850792466</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14">
       <c r="A32">
         <v>81</v>
       </c>
@@ -3138,16 +3105,16 @@
         <v>69</v>
       </c>
       <c r="G32">
-        <v>0.78333333333333333</v>
+        <v>0.7833333333333333</v>
       </c>
       <c r="H32">
-        <v>20791.190512378838</v>
+        <v>20791.19051237884</v>
       </c>
       <c r="I32">
-        <v>0.23360452808255819</v>
+        <v>0.2336045280825582</v>
       </c>
       <c r="J32">
-        <v>1.1235745636762491</v>
+        <v>0.01123574563676249</v>
       </c>
       <c r="K32" t="s">
         <v>337</v>
@@ -3159,10 +3126,10 @@
         <v>63</v>
       </c>
       <c r="N32">
-        <v>4.4732781973255831</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+        <v>4.473278197325583</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33">
         <v>82</v>
       </c>
@@ -3185,13 +3152,13 @@
         <v>1.216666666666667</v>
       </c>
       <c r="H33">
-        <v>20791.190512378838</v>
+        <v>20791.19051237884</v>
       </c>
       <c r="I33">
-        <v>0.45214373123142321</v>
+        <v>0.4521437312314232</v>
       </c>
       <c r="J33">
-        <v>1.7397511930342688</v>
+        <v>0.02174688991292836</v>
       </c>
       <c r="K33" t="s">
         <v>338</v>
@@ -3203,10 +3170,10 @@
         <v>65</v>
       </c>
       <c r="N33">
-        <v>5.5743747686065879</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.574374768606588</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34">
         <v>84</v>
       </c>
@@ -3226,16 +3193,16 @@
         <v>58</v>
       </c>
       <c r="G34">
-        <v>0.36666666666666659</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="H34">
-        <v>20791.190512378838</v>
+        <v>20791.19051237884</v>
       </c>
       <c r="I34">
-        <v>2.24470185365548E-2</v>
+        <v>0.0224470185365548</v>
       </c>
       <c r="J34">
-        <v>1.079640847078482</v>
+        <v>0.001079640847078482</v>
       </c>
       <c r="K34" t="s">
         <v>339</v>
@@ -3247,10 +3214,10 @@
         <v>70</v>
       </c>
       <c r="N34">
-        <v>0.91828712194996931</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+        <v>0.9182871219499693</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35">
         <v>1644</v>
       </c>
@@ -3276,10 +3243,10 @@
         <v>17997.97560650485</v>
       </c>
       <c r="I35">
-        <v>19.859182453452998</v>
+        <v>19.859182453453</v>
       </c>
       <c r="J35">
-        <v>1.4344356139786141</v>
+        <v>1.10341201075278</v>
       </c>
       <c r="K35" t="s">
         <v>340</v>
@@ -3291,10 +3258,10 @@
         <v>30</v>
       </c>
       <c r="N35">
-        <v>5.6471608872378196</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.64716088723782</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36">
         <v>1645</v>
       </c>
@@ -3320,10 +3287,10 @@
         <v>17997.97560650485</v>
       </c>
       <c r="I36">
-        <v>18.179905394799071</v>
+        <v>18.17990539479907</v>
       </c>
       <c r="J36">
-        <v>1.0101083473092649</v>
+        <v>1.010108347309265</v>
       </c>
       <c r="K36" t="s">
         <v>341</v>
@@ -3335,10 +3302,10 @@
         <v>35</v>
       </c>
       <c r="N36">
-        <v>2.8700078679738921</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+        <v>2.870007867973892</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37">
         <v>1658</v>
       </c>
@@ -3364,10 +3331,10 @@
         <v>17997.97560650485</v>
       </c>
       <c r="I37">
-        <v>6.1571918983936174</v>
+        <v>6.157191898393617</v>
       </c>
       <c r="J37">
-        <v>0.85526172957033553</v>
+        <v>0.3421046918281342</v>
       </c>
       <c r="K37" t="s">
         <v>342</v>
@@ -3379,10 +3346,10 @@
         <v>47</v>
       </c>
       <c r="N37">
-        <v>1.7198860051378819</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+        <v>1.719886005137882</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38">
         <v>1659</v>
       </c>
@@ -3402,7 +3369,7 @@
         <v>57</v>
       </c>
       <c r="G38">
-        <v>59.366666666666667</v>
+        <v>59.36666666666667</v>
       </c>
       <c r="H38">
         <v>17997.97560650485</v>
@@ -3411,7 +3378,7 @@
         <v>5.876521910878969</v>
       </c>
       <c r="J38">
-        <v>0.81627540221177297</v>
+        <v>0.3265101608847092</v>
       </c>
       <c r="K38" t="s">
         <v>343</v>
@@ -3423,10 +3390,10 @@
         <v>49</v>
       </c>
       <c r="N38">
-        <v>1.4848034025241641</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+        <v>1.484803402524164</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39">
         <v>1660</v>
       </c>
@@ -3446,16 +3413,16 @@
         <v>57</v>
       </c>
       <c r="G39">
-        <v>60.466666666666669</v>
+        <v>60.46666666666667</v>
       </c>
       <c r="H39">
         <v>17997.97560650485</v>
       </c>
       <c r="I39">
-        <v>5.4621383893342657</v>
+        <v>5.462138389334266</v>
       </c>
       <c r="J39">
-        <v>0.758715661799227</v>
+        <v>0.3034862647196908</v>
       </c>
       <c r="K39" t="s">
         <v>344</v>
@@ -3470,7 +3437,7 @@
         <v>1.354995741565832</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14">
       <c r="A40">
         <v>1661</v>
       </c>
@@ -3496,10 +3463,10 @@
         <v>17997.97560650485</v>
       </c>
       <c r="I40">
-        <v>5.3958555212533632</v>
+        <v>5.395855521253363</v>
       </c>
       <c r="J40">
-        <v>0.74950867242302355</v>
+        <v>0.2998034689692094</v>
       </c>
       <c r="K40" t="s">
         <v>345</v>
@@ -3514,7 +3481,7 @@
         <v>1.014258556626572</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14">
       <c r="A41">
         <v>1662</v>
       </c>
@@ -3534,16 +3501,16 @@
         <v>57</v>
       </c>
       <c r="G41">
-        <v>14.383333333333329</v>
+        <v>14.38333333333333</v>
       </c>
       <c r="H41">
         <v>17997.97560650485</v>
       </c>
       <c r="I41">
-        <v>5.9226299802105524</v>
+        <v>5.922629980210552</v>
       </c>
       <c r="J41">
-        <v>0.82268002103386428</v>
+        <v>0.3290720084135457</v>
       </c>
       <c r="K41" t="s">
         <v>346</v>
@@ -3555,10 +3522,10 @@
         <v>50</v>
       </c>
       <c r="N41">
-        <v>6.1765550199183048</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.176555019918305</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42">
         <v>1663</v>
       </c>
@@ -3578,16 +3545,16 @@
         <v>57</v>
       </c>
       <c r="G42">
-        <v>13.266666666666669</v>
+        <v>13.26666666666667</v>
       </c>
       <c r="H42">
         <v>17997.97560650485</v>
       </c>
       <c r="I42">
-        <v>6.2707537361527006</v>
+        <v>6.270753736152701</v>
       </c>
       <c r="J42">
-        <v>0.87103598110866431</v>
+        <v>0.3484143924434657</v>
       </c>
       <c r="K42" t="s">
         <v>347</v>
@@ -3599,10 +3566,10 @@
         <v>51</v>
       </c>
       <c r="N42">
-        <v>7.0900481941425006</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.090048194142501</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43">
         <v>1664</v>
       </c>
@@ -3622,16 +3589,16 @@
         <v>57</v>
       </c>
       <c r="G43">
-        <v>13.266666666666669</v>
+        <v>13.26666666666667</v>
       </c>
       <c r="H43">
         <v>17997.97560650485</v>
       </c>
       <c r="I43">
-        <v>6.1868509355312433</v>
+        <v>6.186850935531243</v>
       </c>
       <c r="J43">
-        <v>0.8593815036196607</v>
+        <v>0.3437526014478643</v>
       </c>
       <c r="K43" t="s">
         <v>348</v>
@@ -3643,10 +3610,10 @@
         <v>52</v>
       </c>
       <c r="N43">
-        <v>6.9951832185654759</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.995183218565476</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44">
         <v>1665</v>
       </c>
@@ -3675,7 +3642,7 @@
         <v>6.104798849342032</v>
       </c>
       <c r="J44">
-        <v>0.84798409871380598</v>
+        <v>0.3391936394855224</v>
       </c>
       <c r="K44" t="s">
         <v>349</v>
@@ -3687,10 +3654,10 @@
         <v>54</v>
       </c>
       <c r="N44">
-        <v>6.4487311788824293</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.448731178882429</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45">
         <v>1666</v>
       </c>
@@ -3710,16 +3677,16 @@
         <v>57</v>
       </c>
       <c r="G45">
-        <v>13.266666666666669</v>
+        <v>13.26666666666667</v>
       </c>
       <c r="H45">
         <v>17997.97560650485</v>
       </c>
       <c r="I45">
-        <v>5.7803341542226656</v>
+        <v>5.780334154222666</v>
       </c>
       <c r="J45">
-        <v>0.80291448891251016</v>
+        <v>0.3211657955650041</v>
       </c>
       <c r="K45" t="s">
         <v>350</v>
@@ -3731,10 +3698,10 @@
         <v>55</v>
       </c>
       <c r="N45">
-        <v>6.5355536919603008</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.535553691960301</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46">
         <v>1667</v>
       </c>
@@ -3760,10 +3727,10 @@
         <v>17997.97560650485</v>
       </c>
       <c r="I46">
-        <v>5.7858721652504874</v>
+        <v>5.785872165250487</v>
       </c>
       <c r="J46">
-        <v>0.80368374362605421</v>
+        <v>0.3214734974504217</v>
       </c>
       <c r="K46" t="s">
         <v>351</v>
@@ -3778,7 +3745,7 @@
         <v>7.143052055864799</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14">
       <c r="A47">
         <v>1668</v>
       </c>
@@ -3804,10 +3771,10 @@
         <v>17997.97560650485</v>
       </c>
       <c r="I47">
-        <v>5.7959693505329204</v>
+        <v>5.79596935053292</v>
       </c>
       <c r="J47">
-        <v>0.80508628820984407</v>
+        <v>0.3220345152839376</v>
       </c>
       <c r="K47" t="s">
         <v>352</v>
@@ -3819,10 +3786,10 @@
         <v>58</v>
       </c>
       <c r="N47">
-        <v>7.1261918244257227</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.126191824425723</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48">
         <v>1669</v>
       </c>
@@ -3848,10 +3815,10 @@
         <v>17997.97560650485</v>
       </c>
       <c r="I48">
-        <v>5.8605685459993841</v>
+        <v>5.860568545999384</v>
       </c>
       <c r="J48">
-        <v>0.81405940786491171</v>
+        <v>0.3256237631459647</v>
       </c>
       <c r="K48" t="s">
         <v>353</v>
@@ -3863,10 +3830,10 @@
         <v>59</v>
       </c>
       <c r="N48">
-        <v>7.0046636007960759</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.004663600796076</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49">
         <v>1670</v>
       </c>
@@ -3892,10 +3859,10 @@
         <v>17997.97560650485</v>
       </c>
       <c r="I49">
-        <v>5.3353734297005131</v>
+        <v>5.335373429700513</v>
       </c>
       <c r="J49">
-        <v>0.74110743707367255</v>
+        <v>0.296442974829469</v>
       </c>
       <c r="K49" t="s">
         <v>354</v>
@@ -3907,10 +3874,10 @@
         <v>62</v>
       </c>
       <c r="N49">
-        <v>5.5770453968994911</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.577045396899491</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50">
         <v>1671</v>
       </c>
@@ -3930,16 +3897,16 @@
         <v>71</v>
       </c>
       <c r="G50">
-        <v>14.483333333333331</v>
+        <v>14.48333333333333</v>
       </c>
       <c r="H50">
         <v>17997.97560650485</v>
       </c>
       <c r="I50">
-        <v>5.8703512335951364</v>
+        <v>5.870351233595136</v>
       </c>
       <c r="J50">
-        <v>0.81541826730133327</v>
+        <v>0.3261673069205333</v>
       </c>
       <c r="K50" t="s">
         <v>355</v>
@@ -3951,10 +3918,10 @@
         <v>63</v>
       </c>
       <c r="N50">
-        <v>6.0797653742642384</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.079765374264238</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51">
         <v>1672</v>
       </c>
@@ -3980,10 +3947,10 @@
         <v>17997.97560650485</v>
       </c>
       <c r="I51">
-        <v>5.3269334364107097</v>
+        <v>5.32693343641071</v>
       </c>
       <c r="J51">
-        <v>0.73993508393319574</v>
+        <v>0.2959740335732783</v>
       </c>
       <c r="K51" t="s">
         <v>356</v>
@@ -3995,10 +3962,10 @@
         <v>64</v>
       </c>
       <c r="N51">
-        <v>4.7514768015556381</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+        <v>4.751476801555638</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52">
         <v>1673</v>
       </c>
@@ -4027,7 +3994,7 @@
         <v>5.32415833434698</v>
       </c>
       <c r="J52">
-        <v>0.73954960973815276</v>
+        <v>0.2958198438952611</v>
       </c>
       <c r="K52" t="s">
         <v>357</v>
@@ -4039,10 +4006,10 @@
         <v>66</v>
       </c>
       <c r="N52">
-        <v>4.8945275800942616</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+        <v>4.894527580094262</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53">
         <v>1674</v>
       </c>
@@ -4062,7 +4029,7 @@
         <v>68</v>
       </c>
       <c r="G53">
-        <v>16.266666666666669</v>
+        <v>16.26666666666667</v>
       </c>
       <c r="H53">
         <v>17997.97560650485</v>
@@ -4071,7 +4038,7 @@
         <v>5.554465723587013</v>
       </c>
       <c r="J53">
-        <v>0.77154034501240154</v>
+        <v>0.3086161380049606</v>
       </c>
       <c r="K53" t="s">
         <v>358</v>
@@ -4083,10 +4050,10 @@
         <v>68</v>
       </c>
       <c r="N53">
-        <v>5.1219458516683529</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.121945851668353</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54">
         <v>1676</v>
       </c>
@@ -4106,16 +4073,16 @@
         <v>58</v>
       </c>
       <c r="G54">
-        <v>9.1999999999999993</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H54">
         <v>17997.97560650485</v>
       </c>
       <c r="I54">
-        <v>4.0894376977257538</v>
+        <v>4.089437697725754</v>
       </c>
       <c r="J54">
-        <v>0.90886614964579604</v>
+        <v>0.227216537411449</v>
       </c>
       <c r="K54" t="s">
         <v>359</v>
@@ -4127,10 +4094,10 @@
         <v>71</v>
       </c>
       <c r="N54">
-        <v>6.6675614636832936</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.667561463683294</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55">
         <v>1677</v>
       </c>
@@ -4150,16 +4117,16 @@
         <v>56</v>
       </c>
       <c r="G55">
-        <v>10.016666666666669</v>
+        <v>10.01666666666667</v>
       </c>
       <c r="H55">
         <v>17997.97560650485</v>
       </c>
       <c r="I55">
-        <v>4.1279852862293156</v>
+        <v>4.127985286229316</v>
       </c>
       <c r="J55">
-        <v>0.91743324393380676</v>
+        <v>0.2293583109834517</v>
       </c>
       <c r="K55" t="s">
         <v>360</v>
@@ -4171,10 +4138,10 @@
         <v>73</v>
       </c>
       <c r="N55">
-        <v>6.1816751374482246</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.181675137448225</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56">
         <v>1678</v>
       </c>
@@ -4194,16 +4161,16 @@
         <v>53</v>
       </c>
       <c r="G56">
-        <v>8.0666666666666664</v>
+        <v>8.066666666666666</v>
       </c>
       <c r="H56">
         <v>17997.97560650485</v>
       </c>
       <c r="I56">
-        <v>4.1512494859410349</v>
+        <v>4.151249485941035</v>
       </c>
       <c r="J56">
-        <v>0.92260364758816238</v>
+        <v>0.2306509118970406</v>
       </c>
       <c r="K56" t="s">
         <v>361</v>
@@ -4215,10 +4182,10 @@
         <v>75</v>
       </c>
       <c r="N56">
-        <v>7.7192655730308504</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.71926557303085</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
       <c r="A57">
         <v>1679</v>
       </c>
@@ -4238,7 +4205,7 @@
         <v>51</v>
       </c>
       <c r="G57">
-        <v>8.0666666666666664</v>
+        <v>8.066666666666666</v>
       </c>
       <c r="H57">
         <v>17997.97560650485</v>
@@ -4247,7 +4214,7 @@
         <v>3.961454318358097</v>
       </c>
       <c r="J57">
-        <v>0.88042219968924595</v>
+        <v>0.2201055499223115</v>
       </c>
       <c r="K57" t="s">
         <v>362</v>
@@ -4259,10 +4226,10 @@
         <v>77</v>
       </c>
       <c r="N57">
-        <v>7.3663406746328244</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.366340674632824</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58">
         <v>1680</v>
       </c>
@@ -4282,7 +4249,7 @@
         <v>50</v>
       </c>
       <c r="G58">
-        <v>7.0666666666666664</v>
+        <v>7.066666666666666</v>
       </c>
       <c r="H58">
         <v>17997.97560650485</v>
@@ -4291,7 +4258,7 @@
         <v>3.92491800876028</v>
       </c>
       <c r="J58">
-        <v>0.87230210654174523</v>
+        <v>0.2180755266354363</v>
       </c>
       <c r="K58" t="s">
         <v>363</v>
@@ -4306,7 +4273,7 @@
         <v>8.331193886519463</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14">
       <c r="A59">
         <v>1681</v>
       </c>
@@ -4326,16 +4293,16 @@
         <v>50</v>
       </c>
       <c r="G59">
-        <v>3.5333333333333332</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="H59">
         <v>17997.97560650485</v>
       </c>
       <c r="I59">
-        <v>1.1997450142346371</v>
+        <v>1.199745014234637</v>
       </c>
       <c r="J59">
-        <v>0.79991997353370581</v>
+        <v>0.06665999779447548</v>
       </c>
       <c r="K59" t="s">
         <v>364</v>
@@ -4347,10 +4314,10 @@
         <v>81</v>
       </c>
       <c r="N59">
-        <v>5.0932571359017587</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.093257135901759</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60">
         <v>1682</v>
       </c>
@@ -4370,16 +4337,16 @@
         <v>50</v>
       </c>
       <c r="G60">
-        <v>0.78333333333333333</v>
+        <v>0.7833333333333333</v>
       </c>
       <c r="H60">
         <v>17997.97560650485</v>
       </c>
       <c r="I60">
-        <v>0.33036653804451133</v>
+        <v>0.3303665380445113</v>
       </c>
       <c r="J60">
-        <v>0.73423043850578362</v>
+        <v>0.01835576096264459</v>
       </c>
       <c r="K60" t="s">
         <v>365</v>
@@ -4391,10 +4358,10 @@
         <v>83</v>
       </c>
       <c r="N60">
-        <v>6.3261677497885156</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.326167749788516</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61">
         <v>1683</v>
       </c>
@@ -4420,10 +4387,10 @@
         <v>17997.97560650485</v>
       </c>
       <c r="I61">
-        <v>0.30593262365771001</v>
+        <v>0.30593262365771</v>
       </c>
       <c r="J61">
-        <v>0.67992674364363404</v>
+        <v>0.01699816859109085</v>
       </c>
       <c r="K61" t="s">
         <v>366</v>
@@ -4435,10 +4402,10 @@
         <v>85</v>
       </c>
       <c r="N61">
-        <v>7.2457726655773431</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.245772665577343</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
       <c r="A62">
         <v>1689</v>
       </c>
@@ -4461,13 +4428,13 @@
         <v>47.1</v>
       </c>
       <c r="H62">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I62">
-        <v>20.841301103068179</v>
+        <v>20.84130110306818</v>
       </c>
       <c r="J62">
-        <v>1.2227194852746619</v>
+        <v>1.222719485274662</v>
       </c>
       <c r="K62" t="s">
         <v>367</v>
@@ -4479,10 +4446,10 @@
         <v>26</v>
       </c>
       <c r="N62">
-        <v>6.6373570391936862</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.637357039193686</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
       <c r="A63">
         <v>1690</v>
       </c>
@@ -4502,16 +4469,16 @@
         <v>50</v>
       </c>
       <c r="G63">
-        <v>48.983333333333327</v>
+        <v>48.98333333333333</v>
       </c>
       <c r="H63">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I63">
-        <v>21.222976376785141</v>
+        <v>21.22297637678514</v>
       </c>
       <c r="J63">
-        <v>1.2451116474488639</v>
+        <v>1.245111647448864</v>
       </c>
       <c r="K63" t="s">
         <v>368</v>
@@ -4523,10 +4490,10 @@
         <v>28</v>
       </c>
       <c r="N63">
-        <v>6.4990400609413506</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.499040060941351</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
       <c r="A64">
         <v>1691</v>
       </c>
@@ -4549,7 +4516,7 @@
         <v>55.56666666666667</v>
       </c>
       <c r="H64">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I64">
         <v>21.57094741020699</v>
@@ -4567,10 +4534,10 @@
         <v>31</v>
       </c>
       <c r="N64">
-        <v>5.8229912025153832</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.822991202515383</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
       <c r="A65">
         <v>1692</v>
       </c>
@@ -4590,16 +4557,16 @@
         <v>57</v>
       </c>
       <c r="G65">
-        <v>55.983333333333327</v>
+        <v>55.98333333333333</v>
       </c>
       <c r="H65">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I65">
-        <v>20.940725046207412</v>
+        <v>20.94072504620741</v>
       </c>
       <c r="J65">
-        <v>1.2285524988652241</v>
+        <v>1.228552498865224</v>
       </c>
       <c r="K65" t="s">
         <v>370</v>
@@ -4611,10 +4578,10 @@
         <v>32</v>
       </c>
       <c r="N65">
-        <v>5.6107926590016888</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.610792659001689</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
       <c r="A66">
         <v>1693</v>
       </c>
@@ -4634,13 +4601,13 @@
         <v>59</v>
       </c>
       <c r="G66">
-        <v>57.833333333333343</v>
+        <v>57.83333333333334</v>
       </c>
       <c r="H66">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I66">
-        <v>21.117929910074992</v>
+        <v>21.11792991007499</v>
       </c>
       <c r="J66">
         <v>1.238948771097212</v>
@@ -4655,10 +4622,10 @@
         <v>32</v>
       </c>
       <c r="N66">
-        <v>5.4772728873393346</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.477272887339335</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14">
       <c r="A67">
         <v>1694</v>
       </c>
@@ -4678,16 +4645,16 @@
         <v>62</v>
       </c>
       <c r="G67">
-        <v>60.833333333333343</v>
+        <v>60.83333333333334</v>
       </c>
       <c r="H67">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I67">
-        <v>21.619653632859318</v>
+        <v>21.61965363285932</v>
       </c>
       <c r="J67">
-        <v>1.2683839473867879</v>
+        <v>1.268383947386788</v>
       </c>
       <c r="K67" t="s">
         <v>372</v>
@@ -4702,7 +4669,7 @@
         <v>5.330873498513256</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14">
       <c r="A68">
         <v>1695</v>
       </c>
@@ -4722,16 +4689,16 @@
         <v>67</v>
       </c>
       <c r="G68">
-        <v>65.849999999999994</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H68">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I68">
-        <v>20.506089648781309</v>
+        <v>20.50608964878131</v>
       </c>
       <c r="J68">
-        <v>1.2030532669893039</v>
+        <v>1.203053266989304</v>
       </c>
       <c r="K68" t="s">
         <v>373</v>
@@ -4743,10 +4710,10 @@
         <v>34</v>
       </c>
       <c r="N68">
-        <v>4.6710910361688631</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+        <v>4.671091036168863</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
       <c r="A69">
         <v>1696</v>
       </c>
@@ -4766,16 +4733,16 @@
         <v>69</v>
       </c>
       <c r="G69">
-        <v>67.833333333333329</v>
+        <v>67.83333333333333</v>
       </c>
       <c r="H69">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I69">
-        <v>20.532036106591931</v>
+        <v>20.53203610659193</v>
       </c>
       <c r="J69">
-        <v>1.2045754963060831</v>
+        <v>1.204575496306083</v>
       </c>
       <c r="K69" t="s">
         <v>374</v>
@@ -4787,10 +4754,10 @@
         <v>35</v>
       </c>
       <c r="N69">
-        <v>4.5402536845043588</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+        <v>4.540253684504359</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
       <c r="A70">
         <v>1697</v>
       </c>
@@ -4810,16 +4777,16 @@
         <v>69</v>
       </c>
       <c r="G70">
-        <v>67.833333333333329</v>
+        <v>67.83333333333333</v>
       </c>
       <c r="H70">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I70">
-        <v>20.782354876226151</v>
+        <v>20.78235487622615</v>
       </c>
       <c r="J70">
-        <v>1.2192612222906609</v>
+        <v>1.219261222290661</v>
       </c>
       <c r="K70" t="s">
         <v>375</v>
@@ -4831,10 +4798,10 @@
         <v>35</v>
       </c>
       <c r="N70">
-        <v>4.5956067293866196</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+        <v>4.59560672938662</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
       <c r="A71">
         <v>1698</v>
       </c>
@@ -4854,13 +4821,13 @@
         <v>69</v>
       </c>
       <c r="G71">
-        <v>67.833333333333329</v>
+        <v>67.83333333333333</v>
       </c>
       <c r="H71">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I71">
-        <v>21.765587311862319</v>
+        <v>21.76558731186232</v>
       </c>
       <c r="J71">
         <v>1.276945598696001</v>
@@ -4875,10 +4842,10 @@
         <v>36</v>
       </c>
       <c r="N71">
-        <v>4.8130291353012513</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+        <v>4.813029135301251</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
       <c r="A72">
         <v>1699</v>
       </c>
@@ -4898,13 +4865,13 @@
         <v>68</v>
       </c>
       <c r="G72">
-        <v>66.833333333333329</v>
+        <v>66.83333333333333</v>
       </c>
       <c r="H72">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I72">
-        <v>21.100854188515239</v>
+        <v>21.10085418851524</v>
       </c>
       <c r="J72">
         <v>1.237946970999753</v>
@@ -4919,10 +4886,10 @@
         <v>37</v>
       </c>
       <c r="N72">
-        <v>4.7358525610133952</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+        <v>4.735852561013395</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
       <c r="A73">
         <v>1700</v>
       </c>
@@ -4942,13 +4909,13 @@
         <v>50</v>
       </c>
       <c r="G73">
-        <v>48.983333333333327</v>
+        <v>48.98333333333333</v>
       </c>
       <c r="H73">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I73">
-        <v>20.790011914455981</v>
+        <v>20.79001191445598</v>
       </c>
       <c r="J73">
         <v>1.219710446156139</v>
@@ -4963,10 +4930,10 @@
         <v>36</v>
       </c>
       <c r="N73">
-        <v>6.3664548223921003</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.3664548223921</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
       <c r="A74">
         <v>1701</v>
       </c>
@@ -4986,10 +4953,10 @@
         <v>50</v>
       </c>
       <c r="G74">
-        <v>50.633333333333333</v>
+        <v>50.63333333333333</v>
       </c>
       <c r="H74">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I74">
         <v>20.58640160574258</v>
@@ -5007,10 +4974,10 @@
         <v>38</v>
       </c>
       <c r="N74">
-        <v>6.0986706534457937</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.098670653445794</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14">
       <c r="A75">
         <v>1702</v>
       </c>
@@ -5030,13 +4997,13 @@
         <v>60</v>
       </c>
       <c r="G75">
-        <v>58.833333333333343</v>
+        <v>58.83333333333334</v>
       </c>
       <c r="H75">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I75">
-        <v>21.486258637809609</v>
+        <v>21.48625863780961</v>
       </c>
       <c r="J75">
         <v>1.260557916810348</v>
@@ -5051,10 +5018,10 @@
         <v>39</v>
       </c>
       <c r="N75">
-        <v>5.4780829388183134</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.478082938818313</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
       <c r="A76">
         <v>1703</v>
       </c>
@@ -5077,13 +5044,13 @@
         <v>57</v>
       </c>
       <c r="H76">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I76">
-        <v>20.596297765668311</v>
+        <v>20.59629776566831</v>
       </c>
       <c r="J76">
-        <v>1.2083456055866979</v>
+        <v>1.208345605586698</v>
       </c>
       <c r="K76" t="s">
         <v>381</v>
@@ -5095,10 +5062,10 @@
         <v>40</v>
       </c>
       <c r="N76">
-        <v>5.4200783593863973</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.420078359386397</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14">
       <c r="A77">
         <v>1704</v>
       </c>
@@ -5118,10 +5085,10 @@
         <v>58</v>
       </c>
       <c r="G77">
-        <v>56.833333333333343</v>
+        <v>56.83333333333334</v>
       </c>
       <c r="H77">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I77">
         <v>21.3315868497472</v>
@@ -5139,10 +5106,10 @@
         <v>41</v>
       </c>
       <c r="N77">
-        <v>5.6300375849772664</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.630037584977266</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14">
       <c r="A78">
         <v>1723</v>
       </c>
@@ -5162,16 +5129,16 @@
         <v>78</v>
       </c>
       <c r="G78">
-        <v>28.233333333333331</v>
+        <v>28.23333333333333</v>
       </c>
       <c r="H78">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I78">
-        <v>7.8965183151963148</v>
+        <v>7.896518315196315</v>
       </c>
       <c r="J78">
-        <v>0.92654741295373144</v>
+        <v>0.4632737064768657</v>
       </c>
       <c r="K78" t="s">
         <v>383</v>
@@ -5183,10 +5150,10 @@
         <v>67</v>
       </c>
       <c r="N78">
-        <v>4.1953166963852917</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+        <v>4.195316696385292</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
       <c r="A79">
         <v>1724</v>
       </c>
@@ -5206,16 +5173,16 @@
         <v>74</v>
       </c>
       <c r="G79">
-        <v>28.733333333333331</v>
+        <v>28.73333333333333</v>
       </c>
       <c r="H79">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I79">
-        <v>7.4158800608432518</v>
+        <v>7.415880060843252</v>
       </c>
       <c r="J79">
-        <v>0.87015114901036617</v>
+        <v>0.4350755745051831</v>
       </c>
       <c r="K79" t="s">
         <v>384</v>
@@ -5227,10 +5194,10 @@
         <v>69</v>
       </c>
       <c r="N79">
-        <v>3.8713991036884732</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+        <v>3.871399103688473</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14">
       <c r="A80">
         <v>1727</v>
       </c>
@@ -5250,16 +5217,16 @@
         <v>56</v>
       </c>
       <c r="G80">
-        <v>17.516666666666669</v>
+        <v>17.51666666666667</v>
       </c>
       <c r="H80">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I80">
-        <v>7.3762300772332283</v>
+        <v>7.376230077233228</v>
       </c>
       <c r="J80">
-        <v>0.8654987708012476</v>
+        <v>0.4327493854006238</v>
       </c>
       <c r="K80" t="s">
         <v>385</v>
@@ -5271,10 +5238,10 @@
         <v>76</v>
       </c>
       <c r="N80">
-        <v>6.3164672402568094</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.316467240256809</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
       <c r="A81">
         <v>1728</v>
       </c>
@@ -5294,16 +5261,16 @@
         <v>54</v>
       </c>
       <c r="G81">
-        <v>17.516666666666669</v>
+        <v>17.51666666666667</v>
       </c>
       <c r="H81">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I81">
-        <v>7.3734710664709739</v>
+        <v>7.373471066470974</v>
       </c>
       <c r="J81">
-        <v>0.86517503897640535</v>
+        <v>0.4325875194882027</v>
       </c>
       <c r="K81" t="s">
         <v>386</v>
@@ -5315,10 +5282,10 @@
         <v>78</v>
       </c>
       <c r="N81">
-        <v>6.3141046239998824</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.314104623999882</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14">
       <c r="A82">
         <v>1729</v>
       </c>
@@ -5338,16 +5305,16 @@
         <v>54</v>
       </c>
       <c r="G82">
-        <v>17.516666666666669</v>
+        <v>17.51666666666667</v>
       </c>
       <c r="H82">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I82">
-        <v>7.3762300772332283</v>
+        <v>7.376230077233228</v>
       </c>
       <c r="J82">
-        <v>0.8654987708012476</v>
+        <v>0.4327493854006238</v>
       </c>
       <c r="K82" t="s">
         <v>387</v>
@@ -5359,10 +5326,10 @@
         <v>80</v>
       </c>
       <c r="N82">
-        <v>6.3164672402568094</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.316467240256809</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14">
       <c r="A83">
         <v>1730</v>
       </c>
@@ -5382,16 +5349,16 @@
         <v>52</v>
       </c>
       <c r="G83">
-        <v>16.516666666666669</v>
+        <v>16.51666666666667</v>
       </c>
       <c r="H83">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I83">
-        <v>7.3738203392276409</v>
+        <v>7.373820339227641</v>
       </c>
       <c r="J83">
-        <v>0.86521602131269437</v>
+        <v>0.4326080106563472</v>
       </c>
       <c r="K83" t="s">
         <v>388</v>
@@ -5403,10 +5370,10 @@
         <v>82</v>
       </c>
       <c r="N83">
-        <v>6.6967086834559817</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.696708683455982</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14">
       <c r="A84">
         <v>1731</v>
       </c>
@@ -5426,16 +5393,16 @@
         <v>52</v>
       </c>
       <c r="G84">
-        <v>16.516666666666669</v>
+        <v>16.51666666666667</v>
       </c>
       <c r="H84">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I84">
-        <v>7.4192108745078436</v>
+        <v>7.419210874507844</v>
       </c>
       <c r="J84">
-        <v>0.87054197401206601</v>
+        <v>0.435270987006033</v>
       </c>
       <c r="K84" t="s">
         <v>389</v>
@@ -5447,10 +5414,10 @@
         <v>84</v>
       </c>
       <c r="N84">
-        <v>6.7379311675651463</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.737931167565146</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
       <c r="A85">
         <v>1732</v>
       </c>
@@ -5470,16 +5437,16 @@
         <v>52</v>
       </c>
       <c r="G85">
-        <v>16.516666666666669</v>
+        <v>16.51666666666667</v>
       </c>
       <c r="H85">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I85">
-        <v>7.3738203392276409</v>
+        <v>7.373820339227641</v>
       </c>
       <c r="J85">
-        <v>0.86521602131269437</v>
+        <v>0.4326080106563472</v>
       </c>
       <c r="K85" t="s">
         <v>390</v>
@@ -5491,10 +5458,10 @@
         <v>86</v>
       </c>
       <c r="N85">
-        <v>6.6967086834559817</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.696708683455982</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14">
       <c r="A86">
         <v>1733</v>
       </c>
@@ -5514,16 +5481,16 @@
         <v>52</v>
       </c>
       <c r="G86">
-        <v>16.516666666666669</v>
+        <v>16.51666666666667</v>
       </c>
       <c r="H86">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I86">
-        <v>7.3500960542328908</v>
+        <v>7.350096054232891</v>
       </c>
       <c r="J86">
-        <v>0.86243230398201198</v>
+        <v>0.431216151991006</v>
       </c>
       <c r="K86" t="s">
         <v>391</v>
@@ -5535,10 +5502,10 @@
         <v>88</v>
       </c>
       <c r="N86">
-        <v>6.6751629150450071</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.675162915045007</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14">
       <c r="A87">
         <v>1734</v>
       </c>
@@ -5558,16 +5525,16 @@
         <v>49</v>
       </c>
       <c r="G87">
-        <v>16.516666666666669</v>
+        <v>16.51666666666667</v>
       </c>
       <c r="H87">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I87">
-        <v>7.3741735502848433</v>
+        <v>7.374173550284843</v>
       </c>
       <c r="J87">
-        <v>0.86525746575418305</v>
+        <v>0.4326287328770915</v>
       </c>
       <c r="K87" t="s">
         <v>392</v>
@@ -5579,10 +5546,10 @@
         <v>90</v>
       </c>
       <c r="N87">
-        <v>6.6970294603999596</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.69702946039996</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14">
       <c r="A88">
         <v>1735</v>
       </c>
@@ -5602,16 +5569,16 @@
         <v>47</v>
       </c>
       <c r="G88">
-        <v>15.516666666666669</v>
+        <v>15.51666666666667</v>
       </c>
       <c r="H88">
-        <v>17045.038828661949</v>
+        <v>17045.03882866195</v>
       </c>
       <c r="I88">
-        <v>7.3583601930421034</v>
+        <v>7.358360193042103</v>
       </c>
       <c r="J88">
-        <v>0.86340198658494216</v>
+        <v>0.4317009932924711</v>
       </c>
       <c r="K88" t="s">
         <v>393</v>
@@ -5623,10 +5590,10 @@
         <v>92</v>
       </c>
       <c r="N88">
-        <v>7.1133449771620754</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.113344977162075</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14">
       <c r="A89">
         <v>1905</v>
       </c>
@@ -5646,16 +5613,16 @@
         <v>24</v>
       </c>
       <c r="G89">
-        <v>28.833333333333329</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="H89">
-        <v>13527.247980897489</v>
+        <v>13527.24798089749</v>
       </c>
       <c r="I89">
-        <v>12.958360242612279</v>
+        <v>12.95836024261228</v>
       </c>
       <c r="J89">
-        <v>0.95794504994004981</v>
+        <v>0.9579450499400498</v>
       </c>
       <c r="K89" t="s">
         <v>394</v>
@@ -5667,10 +5634,10 @@
         <v>30</v>
       </c>
       <c r="N89">
-        <v>6.7413434788156366</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.741343478815637</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14">
       <c r="A90">
         <v>1906</v>
       </c>
@@ -5693,13 +5660,13 @@
         <v>26.65</v>
       </c>
       <c r="H90">
-        <v>13527.247980897489</v>
+        <v>13527.24798089749</v>
       </c>
       <c r="I90">
-        <v>12.536150082827669</v>
+        <v>12.53615008282767</v>
       </c>
       <c r="J90">
-        <v>0.92673322027736926</v>
+        <v>0.9267332202773693</v>
       </c>
       <c r="K90" t="s">
         <v>395</v>
@@ -5711,10 +5678,10 @@
         <v>34</v>
       </c>
       <c r="N90">
-        <v>7.0559944181018768</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.055994418101877</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14">
       <c r="A91">
         <v>1907</v>
       </c>
@@ -5737,13 +5704,13 @@
         <v>22.18333333333333</v>
       </c>
       <c r="H91">
-        <v>13527.247980897489</v>
+        <v>13527.24798089749</v>
       </c>
       <c r="I91">
         <v>12.46147441636732</v>
       </c>
       <c r="J91">
-        <v>0.92121283160956347</v>
+        <v>0.9212128316095635</v>
       </c>
       <c r="K91" t="s">
         <v>396</v>
@@ -5755,10 +5722,10 @@
         <v>38</v>
       </c>
       <c r="N91">
-        <v>8.4262411530658063</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+        <v>8.426241153065806</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14">
       <c r="A92">
         <v>1908</v>
       </c>
@@ -5778,16 +5745,16 @@
         <v>24</v>
       </c>
       <c r="G92">
-        <v>22.166666666666671</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="H92">
-        <v>13527.247980897489</v>
+        <v>13527.24798089749</v>
       </c>
       <c r="I92">
         <v>12.61980922284177</v>
       </c>
       <c r="J92">
-        <v>0.93291771102761245</v>
+        <v>0.9329177110276125</v>
       </c>
       <c r="K92" t="s">
         <v>397</v>
@@ -5799,10 +5766,10 @@
         <v>42</v>
       </c>
       <c r="N92">
-        <v>8.5397205267350351</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+        <v>8.539720526735035</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14">
       <c r="A93">
         <v>1909</v>
       </c>
@@ -5825,13 +5792,13 @@
         <v>22.18333333333333</v>
       </c>
       <c r="H93">
-        <v>13527.247980897489</v>
+        <v>13527.24798089749</v>
       </c>
       <c r="I93">
         <v>12.35973114698713</v>
       </c>
       <c r="J93">
-        <v>0.91369147401163431</v>
+        <v>0.9136914740116343</v>
       </c>
       <c r="K93" t="s">
         <v>398</v>
@@ -5843,10 +5810,10 @@
         <v>46</v>
       </c>
       <c r="N93">
-        <v>8.3574440513060964</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+        <v>8.357444051306096</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14">
       <c r="A94">
         <v>1910</v>
       </c>
@@ -5866,13 +5833,13 @@
         <v>24</v>
       </c>
       <c r="G94">
-        <v>22.133333333333329</v>
+        <v>22.13333333333333</v>
       </c>
       <c r="H94">
-        <v>13527.247980897489</v>
+        <v>13527.24798089749</v>
       </c>
       <c r="I94">
-        <v>12.028394746079959</v>
+        <v>12.02839474607996</v>
       </c>
       <c r="J94">
         <v>0.8891974748349305</v>
@@ -5887,10 +5854,10 @@
         <v>50</v>
       </c>
       <c r="N94">
-        <v>8.1517735477951501</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+        <v>8.15177354779515</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14">
       <c r="A95">
         <v>1911</v>
       </c>
@@ -5910,16 +5877,16 @@
         <v>24</v>
       </c>
       <c r="G95">
-        <v>22.166666666666671</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="H95">
-        <v>13527.247980897489</v>
+        <v>13527.24798089749</v>
       </c>
       <c r="I95">
-        <v>12.395009014159159</v>
+        <v>12.39500901415916</v>
       </c>
       <c r="J95">
-        <v>0.91629938562986191</v>
+        <v>0.9162993856298619</v>
       </c>
       <c r="K95" t="s">
         <v>400</v>
@@ -5931,10 +5898,10 @@
         <v>54</v>
       </c>
       <c r="N95">
-        <v>8.3876000847693533</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+        <v>8.387600084769353</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14">
       <c r="A96">
         <v>1912</v>
       </c>
@@ -5954,16 +5921,16 @@
         <v>24</v>
       </c>
       <c r="G96">
-        <v>22.166666666666671</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="H96">
-        <v>13527.247980897489</v>
+        <v>13527.24798089749</v>
       </c>
       <c r="I96">
         <v>12.21880087515372</v>
       </c>
       <c r="J96">
-        <v>0.90327322249200326</v>
+        <v>0.9032732224920033</v>
       </c>
       <c r="K96" t="s">
         <v>401</v>
@@ -5975,10 +5942,10 @@
         <v>58</v>
       </c>
       <c r="N96">
-        <v>8.2683614944649211</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+        <v>8.268361494464921</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14">
       <c r="A97">
         <v>1913</v>
       </c>
@@ -6001,13 +5968,13 @@
         <v>22.1</v>
       </c>
       <c r="H97">
-        <v>13527.247980897489</v>
+        <v>13527.24798089749</v>
       </c>
       <c r="I97">
-        <v>12.370431579034239</v>
+        <v>12.37043157903424</v>
       </c>
       <c r="J97">
-        <v>0.91448250202133885</v>
+        <v>0.9144825020213389</v>
       </c>
       <c r="K97" t="s">
         <v>402</v>
@@ -6019,10 +5986,10 @@
         <v>62</v>
       </c>
       <c r="N97">
-        <v>8.3962205287562668</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+        <v>8.396220528756267</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14">
       <c r="A98">
         <v>1914</v>
       </c>
@@ -6042,16 +6009,16 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>25.533333333333331</v>
+        <v>25.53333333333333</v>
       </c>
       <c r="H98">
-        <v>13527.247980897489</v>
+        <v>13527.24798089749</v>
       </c>
       <c r="I98">
-        <v>12.261464743708339</v>
+        <v>12.26146474370834</v>
       </c>
       <c r="J98">
-        <v>0.90642714327580765</v>
+        <v>0.9064271432758076</v>
       </c>
       <c r="K98" t="s">
         <v>403</v>
@@ -6066,7 +6033,7 @@
         <v>7.203210358575399</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14">
       <c r="A99">
         <v>1915</v>
       </c>
@@ -6086,13 +6053,13 @@
         <v>24</v>
       </c>
       <c r="G99">
-        <v>22.166666666666671</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="H99">
-        <v>13527.247980897489</v>
+        <v>13527.24798089749</v>
       </c>
       <c r="I99">
-        <v>12.491133309833399</v>
+        <v>12.4911333098334</v>
       </c>
       <c r="J99">
         <v>0.923405361347169</v>
@@ -6107,10 +6074,10 @@
         <v>70</v>
       </c>
       <c r="N99">
-        <v>8.4526466006391452</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+        <v>8.452646600639145</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14">
       <c r="A100">
         <v>1916</v>
       </c>
@@ -6130,16 +6097,16 @@
         <v>24</v>
       </c>
       <c r="G100">
-        <v>22.166666666666671</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="H100">
-        <v>13527.247980897489</v>
+        <v>13527.24798089749</v>
       </c>
       <c r="I100">
         <v>12.31312863881625</v>
       </c>
       <c r="J100">
-        <v>0.91024638982032746</v>
+        <v>0.9102463898203275</v>
       </c>
       <c r="K100" t="s">
         <v>405</v>
@@ -6151,10 +6118,10 @@
         <v>74</v>
       </c>
       <c r="N100">
-        <v>8.3321923119809203</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+        <v>8.33219231198092</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14">
       <c r="A101">
         <v>1917</v>
       </c>
@@ -6174,16 +6141,16 @@
         <v>24</v>
       </c>
       <c r="G101">
-        <v>22.166666666666671</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="H101">
-        <v>13527.247980897489</v>
+        <v>13527.24798089749</v>
       </c>
       <c r="I101">
-        <v>12.618616551600301</v>
+        <v>12.6186165516003</v>
       </c>
       <c r="J101">
-        <v>0.93282954296540521</v>
+        <v>0.9328295429654052</v>
       </c>
       <c r="K101" t="s">
         <v>406</v>
@@ -6195,10 +6162,10 @@
         <v>78</v>
       </c>
       <c r="N101">
-        <v>8.5389134559701283</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+        <v>8.538913455970128</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14">
       <c r="A102">
         <v>1921</v>
       </c>
@@ -6218,16 +6185,16 @@
         <v>25</v>
       </c>
       <c r="G102">
-        <v>24.033333333333331</v>
+        <v>24.03333333333333</v>
       </c>
       <c r="H102">
-        <v>13375.884707038051</v>
+        <v>13375.88470703805</v>
       </c>
       <c r="I102">
-        <v>15.956040924314131</v>
+        <v>15.95604092431413</v>
       </c>
       <c r="J102">
-        <v>1.1928961166896479</v>
+        <v>1.192896116689648</v>
       </c>
       <c r="K102" t="s">
         <v>407</v>
@@ -6239,10 +6206,10 @@
         <v>54</v>
       </c>
       <c r="N102">
-        <v>9.9586940581710977</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+        <v>9.958694058171098</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14">
       <c r="A103">
         <v>1922</v>
       </c>
@@ -6262,16 +6229,16 @@
         <v>25</v>
       </c>
       <c r="G103">
-        <v>21.716666666666669</v>
+        <v>21.71666666666667</v>
       </c>
       <c r="H103">
-        <v>13375.884707038051</v>
+        <v>13375.88470703805</v>
       </c>
       <c r="I103">
         <v>15.46987516635315</v>
       </c>
       <c r="J103">
-        <v>1.1565496791560479</v>
+        <v>1.156549679156048</v>
       </c>
       <c r="K103" t="s">
         <v>408</v>
@@ -6283,10 +6250,10 @@
         <v>54</v>
       </c>
       <c r="N103">
-        <v>10.685255295255439</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+        <v>10.68525529525544</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14">
       <c r="A104">
         <v>1923</v>
       </c>
@@ -6306,16 +6273,16 @@
         <v>25</v>
       </c>
       <c r="G104">
-        <v>23.866666666666671</v>
+        <v>23.86666666666667</v>
       </c>
       <c r="H104">
-        <v>13375.884707038051</v>
+        <v>13375.88470703805</v>
       </c>
       <c r="I104">
         <v>15.55769316686173</v>
       </c>
       <c r="J104">
-        <v>1.1631150766928839</v>
+        <v>1.163115076692884</v>
       </c>
       <c r="K104" t="s">
         <v>409</v>
@@ -6327,10 +6294,10 @@
         <v>58</v>
       </c>
       <c r="N104">
-        <v>9.7778797836421507</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+        <v>9.777879783642151</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14">
       <c r="A105">
         <v>1924</v>
       </c>
@@ -6350,10 +6317,10 @@
         <v>25</v>
       </c>
       <c r="G105">
-        <v>20.466666666666669</v>
+        <v>20.46666666666667</v>
       </c>
       <c r="H105">
-        <v>13375.884707038051</v>
+        <v>13375.88470703805</v>
       </c>
       <c r="I105">
         <v>15.11880996380579</v>
@@ -6374,7 +6341,7 @@
         <v>11.08056104839187</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:14">
       <c r="A106">
         <v>1925</v>
       </c>
@@ -6394,10 +6361,10 @@
         <v>25</v>
       </c>
       <c r="G106">
-        <v>22.316666666666659</v>
+        <v>22.31666666666666</v>
       </c>
       <c r="H106">
-        <v>13375.884707038051</v>
+        <v>13375.88470703805</v>
       </c>
       <c r="I106">
         <v>15.50371508527553</v>
@@ -6415,10 +6382,10 @@
         <v>62</v>
       </c>
       <c r="N106">
-        <v>10.420719624158311</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
+        <v>10.42071962415831</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14">
       <c r="A107">
         <v>1926</v>
       </c>
@@ -6438,16 +6405,16 @@
         <v>25</v>
       </c>
       <c r="G107">
-        <v>20.466666666666669</v>
+        <v>20.46666666666667</v>
       </c>
       <c r="H107">
-        <v>13375.884707038051</v>
+        <v>13375.88470703805</v>
       </c>
       <c r="I107">
         <v>15.34637467128108</v>
       </c>
       <c r="J107">
-        <v>1.1473166080151851</v>
+        <v>1.147316608015185</v>
       </c>
       <c r="K107" t="s">
         <v>412</v>
@@ -6462,7 +6429,7 @@
         <v>11.24734300012457</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:14">
       <c r="A108">
         <v>1927</v>
       </c>
@@ -6482,16 +6449,16 @@
         <v>27</v>
       </c>
       <c r="G108">
-        <v>25.016666666666669</v>
+        <v>25.01666666666667</v>
       </c>
       <c r="H108">
-        <v>13375.884707038051</v>
+        <v>13375.88470703805</v>
       </c>
       <c r="I108">
         <v>15.62352696692624</v>
       </c>
       <c r="J108">
-        <v>1.1680369044079411</v>
+        <v>1.168036904407941</v>
       </c>
       <c r="K108" t="s">
         <v>413</v>
@@ -6503,10 +6470,10 @@
         <v>65</v>
       </c>
       <c r="N108">
-        <v>9.3678709328671665</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+        <v>9.367870932867167</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14">
       <c r="A109">
         <v>1928</v>
       </c>
@@ -6526,16 +6493,16 @@
         <v>25</v>
       </c>
       <c r="G109">
-        <v>20.966666666666669</v>
+        <v>20.96666666666667</v>
       </c>
       <c r="H109">
-        <v>13375.884707038051</v>
+        <v>13375.88470703805</v>
       </c>
       <c r="I109">
         <v>15.64304857697379</v>
       </c>
       <c r="J109">
-        <v>1.1694963674995511</v>
+        <v>1.169496367499551</v>
       </c>
       <c r="K109" t="s">
         <v>414</v>
@@ -6550,7 +6517,7 @@
         <v>11.19137020610208</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:14">
       <c r="A110">
         <v>1929</v>
       </c>
@@ -6570,16 +6537,16 @@
         <v>29</v>
       </c>
       <c r="G110">
-        <v>20.416666666666671</v>
+        <v>20.41666666666667</v>
       </c>
       <c r="H110">
-        <v>13375.884707038051</v>
+        <v>13375.88470703805</v>
       </c>
       <c r="I110">
         <v>15.26025960063104</v>
       </c>
       <c r="J110">
-        <v>1.1408785239156169</v>
+        <v>1.140878523915617</v>
       </c>
       <c r="K110" t="s">
         <v>415</v>
@@ -6591,10 +6558,10 @@
         <v>69</v>
       </c>
       <c r="N110">
-        <v>11.211619298422811</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+        <v>11.21161929842281</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14">
       <c r="A111">
         <v>1930</v>
       </c>
@@ -6614,16 +6581,16 @@
         <v>25</v>
       </c>
       <c r="G111">
-        <v>21.283333333333331</v>
+        <v>21.28333333333333</v>
       </c>
       <c r="H111">
-        <v>13375.884707038051</v>
+        <v>13375.88470703805</v>
       </c>
       <c r="I111">
         <v>15.33684072752312</v>
       </c>
       <c r="J111">
-        <v>1.1466038369374749</v>
+        <v>1.146603836937475</v>
       </c>
       <c r="K111" t="s">
         <v>416</v>
@@ -6638,7 +6605,7 @@
         <v>10.80904984711888</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:14">
       <c r="A112">
         <v>1931</v>
       </c>
@@ -6658,13 +6625,13 @@
         <v>26</v>
       </c>
       <c r="G112">
-        <v>20.066666666666659</v>
+        <v>20.06666666666666</v>
       </c>
       <c r="H112">
-        <v>13375.884707038051</v>
+        <v>13375.88470703805</v>
       </c>
       <c r="I112">
-        <v>15.176958291333881</v>
+        <v>15.17695829133388</v>
       </c>
       <c r="J112">
         <v>1.134650800582047</v>
@@ -6682,7 +6649,7 @@
         <v>11.34490237724293</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:14">
       <c r="A113">
         <v>1932</v>
       </c>
@@ -6702,16 +6669,16 @@
         <v>25</v>
       </c>
       <c r="G113">
-        <v>21.466666666666669</v>
+        <v>21.46666666666667</v>
       </c>
       <c r="H113">
-        <v>13375.884707038051</v>
+        <v>13375.88470703805</v>
       </c>
       <c r="I113">
         <v>15.32198444542669</v>
       </c>
       <c r="J113">
-        <v>1.1454931603413609</v>
+        <v>1.145493160341361</v>
       </c>
       <c r="K113" t="s">
         <v>418</v>
@@ -6726,7 +6693,7 @@
         <v>10.70635559074846</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:14">
       <c r="A114">
         <v>1933</v>
       </c>
@@ -6749,10 +6716,10 @@
         <v>21</v>
       </c>
       <c r="H114">
-        <v>13375.884707038051</v>
+        <v>13375.88470703805</v>
       </c>
       <c r="I114">
-        <v>15.442474853174391</v>
+        <v>15.44247485317439</v>
       </c>
       <c r="J114">
         <v>1.154501193109787</v>
@@ -6767,10 +6734,10 @@
         <v>77</v>
       </c>
       <c r="N114">
-        <v>11.030339180838849</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
+        <v>11.03033918083885</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14">
       <c r="A115">
         <v>2179</v>
       </c>
@@ -6793,10 +6760,10 @@
         <v>28</v>
       </c>
       <c r="H115">
-        <v>7485.4907029589904</v>
+        <v>7485.49070295899</v>
       </c>
       <c r="I115">
-        <v>9.5586402939967563</v>
+        <v>9.558640293996756</v>
       </c>
       <c r="J115">
         <v>1.276955736544868</v>
@@ -6811,10 +6778,10 @@
         <v>32</v>
       </c>
       <c r="N115">
-        <v>5.1207001574982618</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.120700157498262</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14">
       <c r="A116">
         <v>2180</v>
       </c>
@@ -6834,16 +6801,16 @@
         <v>19</v>
       </c>
       <c r="G116">
-        <v>18.600000000000001</v>
+        <v>18.6</v>
       </c>
       <c r="H116">
-        <v>7485.4907029589904</v>
+        <v>7485.49070295899</v>
       </c>
       <c r="I116">
-        <v>9.5017048538588487</v>
+        <v>9.501704853858849</v>
       </c>
       <c r="J116">
-        <v>1.2693496299585081</v>
+        <v>1.269349629958508</v>
       </c>
       <c r="K116" t="s">
         <v>421</v>
@@ -6855,10 +6822,10 @@
         <v>33</v>
       </c>
       <c r="N116">
-        <v>7.6626652047248784</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.662665204724878</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14">
       <c r="A117">
         <v>2181</v>
       </c>
@@ -6881,13 +6848,13 @@
         <v>27.1</v>
       </c>
       <c r="H117">
-        <v>7485.4907029589904</v>
+        <v>7485.49070295899</v>
       </c>
       <c r="I117">
-        <v>9.9010833212606641</v>
+        <v>9.901083321260664</v>
       </c>
       <c r="J117">
-        <v>1.3227033088621429</v>
+        <v>1.322703308862143</v>
       </c>
       <c r="K117" t="s">
         <v>422</v>
@@ -6899,10 +6866,10 @@
         <v>33</v>
       </c>
       <c r="N117">
-        <v>5.4803044213619909</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.480304421361991</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14">
       <c r="A118">
         <v>2182</v>
       </c>
@@ -6922,13 +6889,13 @@
         <v>27</v>
       </c>
       <c r="G118">
-        <v>26.216666666666669</v>
+        <v>26.21666666666667</v>
       </c>
       <c r="H118">
-        <v>7485.4907029589904</v>
+        <v>7485.49070295899</v>
       </c>
       <c r="I118">
-        <v>9.9489868334767806</v>
+        <v>9.948986833476781</v>
       </c>
       <c r="J118">
         <v>1.329102824153396</v>
@@ -6946,7 +6913,7 @@
         <v>5.692363731804897</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:14">
       <c r="A119">
         <v>2183</v>
       </c>
@@ -6966,10 +6933,10 @@
         <v>25</v>
       </c>
       <c r="G119">
-        <v>24.216666666666669</v>
+        <v>24.21666666666667</v>
       </c>
       <c r="H119">
-        <v>7485.4907029589904</v>
+        <v>7485.49070295899</v>
       </c>
       <c r="I119">
         <v>9.390381788719754</v>
@@ -6990,7 +6957,7 @@
         <v>5.816478740432057</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:14">
       <c r="A120">
         <v>2218</v>
       </c>
@@ -7010,16 +6977,16 @@
         <v>26</v>
       </c>
       <c r="G120">
-        <v>24.983333333333331</v>
+        <v>24.98333333333333</v>
       </c>
       <c r="H120">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I120">
         <v>10.60451599673752</v>
       </c>
       <c r="J120">
-        <v>1.2205598533167941</v>
+        <v>1.220559853316794</v>
       </c>
       <c r="K120" t="s">
         <v>425</v>
@@ -7031,10 +6998,10 @@
         <v>30</v>
       </c>
       <c r="N120">
-        <v>6.3669542341986478</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.366954234198648</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14">
       <c r="A121">
         <v>2219</v>
       </c>
@@ -7057,7 +7024,7 @@
         <v>24.75</v>
       </c>
       <c r="H121">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I121">
         <v>10.00819654364412</v>
@@ -7078,7 +7045,7 @@
         <v>6.065573662814618</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:14">
       <c r="A122">
         <v>2220</v>
       </c>
@@ -7098,16 +7065,16 @@
         <v>26</v>
       </c>
       <c r="G122">
-        <v>25.083333333333329</v>
+        <v>25.08333333333333</v>
       </c>
       <c r="H122">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I122">
         <v>11.03075946101788</v>
       </c>
       <c r="J122">
-        <v>1.2696196746607691</v>
+        <v>1.269619674660769</v>
       </c>
       <c r="K122" t="s">
         <v>427</v>
@@ -7122,7 +7089,7 @@
         <v>6.596467451771491</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:14">
       <c r="A123">
         <v>2221</v>
       </c>
@@ -7145,13 +7112,13 @@
         <v>25.95</v>
       </c>
       <c r="H123">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I123">
-        <v>10.198389416840021</v>
+        <v>10.19838941684002</v>
       </c>
       <c r="J123">
-        <v>1.1738154475428531</v>
+        <v>1.173815447542853</v>
       </c>
       <c r="K123" t="s">
         <v>428</v>
@@ -7163,10 +7130,10 @@
         <v>33</v>
       </c>
       <c r="N123">
-        <v>5.8950227843005916</v>
-      </c>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.895022784300592</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14">
       <c r="A124">
         <v>2222</v>
       </c>
@@ -7189,10 +7156,10 @@
         <v>25.75</v>
       </c>
       <c r="H124">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I124">
-        <v>9.3304435404791288</v>
+        <v>9.330443540479129</v>
       </c>
       <c r="J124">
         <v>1.073916509027989</v>
@@ -7207,10 +7174,10 @@
         <v>34</v>
       </c>
       <c r="N124">
-        <v>5.4352098294053173</v>
-      </c>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.435209829405317</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14">
       <c r="A125">
         <v>2223</v>
       </c>
@@ -7230,16 +7197,16 @@
         <v>26</v>
       </c>
       <c r="G125">
-        <v>25.733333333333331</v>
+        <v>25.73333333333333</v>
       </c>
       <c r="H125">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I125">
-        <v>10.012632255329679</v>
+        <v>10.01263225532968</v>
       </c>
       <c r="J125">
-        <v>1.1524351475013079</v>
+        <v>1.152435147501308</v>
       </c>
       <c r="K125" t="s">
         <v>430</v>
@@ -7251,10 +7218,10 @@
         <v>35</v>
       </c>
       <c r="N125">
-        <v>5.8363789053087496</v>
-      </c>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
+        <v>5.83637890530875</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14">
       <c r="A126">
         <v>2224</v>
       </c>
@@ -7274,13 +7241,13 @@
         <v>25</v>
       </c>
       <c r="G126">
-        <v>23.733333333333331</v>
+        <v>23.73333333333333</v>
       </c>
       <c r="H126">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I126">
-        <v>9.6044220243332639</v>
+        <v>9.604422024333264</v>
       </c>
       <c r="J126">
         <v>1.105450917403425</v>
@@ -7295,10 +7262,10 @@
         <v>36</v>
       </c>
       <c r="N126">
-        <v>6.0702105490870348</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.070210549087035</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14">
       <c r="A127">
         <v>2225</v>
       </c>
@@ -7321,10 +7288,10 @@
         <v>33.5</v>
       </c>
       <c r="H127">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I127">
-        <v>8.9752301557461447</v>
+        <v>8.975230155746145</v>
       </c>
       <c r="J127">
         <v>1.033032116293872</v>
@@ -7339,10 +7306,10 @@
         <v>38</v>
       </c>
       <c r="N127">
-        <v>4.0187597712296173</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
+        <v>4.018759771229617</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14">
       <c r="A128">
         <v>2226</v>
       </c>
@@ -7362,16 +7329,16 @@
         <v>24</v>
       </c>
       <c r="G128">
-        <v>28.633333333333329</v>
+        <v>28.63333333333333</v>
       </c>
       <c r="H128">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I128">
-        <v>9.4494982494079203</v>
+        <v>9.44949824940792</v>
       </c>
       <c r="J128">
-        <v>1.0876194821869249</v>
+        <v>1.087619482186925</v>
       </c>
       <c r="K128" t="s">
         <v>433</v>
@@ -7383,10 +7350,10 @@
         <v>39</v>
       </c>
       <c r="N128">
-        <v>4.9502610154057782</v>
-      </c>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
+        <v>4.950261015405778</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14">
       <c r="A129">
         <v>2234</v>
       </c>
@@ -7406,16 +7373,16 @@
         <v>25</v>
       </c>
       <c r="G129">
-        <v>19.966666666666669</v>
+        <v>19.96666666666667</v>
       </c>
       <c r="H129">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I129">
-        <v>9.1540874879282281</v>
+        <v>9.154087487928228</v>
       </c>
       <c r="J129">
-        <v>1.0536182589523351</v>
+        <v>1.053618258952335</v>
       </c>
       <c r="K129" t="s">
         <v>434</v>
@@ -7427,10 +7394,10 @@
         <v>53</v>
       </c>
       <c r="N129">
-        <v>6.8770273281597714</v>
-      </c>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.877027328159771</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14">
       <c r="A130">
         <v>2236</v>
       </c>
@@ -7453,10 +7420,10 @@
         <v>12.5</v>
       </c>
       <c r="H130">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I130">
-        <v>8.1899197366604994</v>
+        <v>8.189919736660499</v>
       </c>
       <c r="J130">
         <v>0.9426443635456826</v>
@@ -7471,10 +7438,10 @@
         <v>56</v>
       </c>
       <c r="N130">
-        <v>9.8279036839925986</v>
-      </c>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
+        <v>9.827903683992599</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14">
       <c r="A131">
         <v>2237</v>
       </c>
@@ -7497,10 +7464,10 @@
         <v>12.5</v>
       </c>
       <c r="H131">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I131">
-        <v>8.1899197366604994</v>
+        <v>8.189919736660499</v>
       </c>
       <c r="J131">
         <v>0.9426443635456826</v>
@@ -7515,10 +7482,10 @@
         <v>58</v>
       </c>
       <c r="N131">
-        <v>9.8279036839925986</v>
-      </c>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
+        <v>9.827903683992599</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14">
       <c r="A132">
         <v>2238</v>
       </c>
@@ -7538,16 +7505,16 @@
         <v>27</v>
       </c>
       <c r="G132">
-        <v>8.1666666666666661</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="H132">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I132">
-        <v>4.3642655055272934</v>
+        <v>4.364265505527293</v>
       </c>
       <c r="J132">
-        <v>1.0046375085672439</v>
+        <v>0.5023187542836219</v>
       </c>
       <c r="K132" t="s">
         <v>437</v>
@@ -7559,10 +7526,10 @@
         <v>60</v>
       </c>
       <c r="N132">
-        <v>8.0159978672950274</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
+        <v>8.015997867295027</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14">
       <c r="A133">
         <v>2241</v>
       </c>
@@ -7582,16 +7549,16 @@
         <v>31</v>
       </c>
       <c r="G133">
-        <v>7.1333333333333337</v>
+        <v>7.133333333333334</v>
       </c>
       <c r="H133">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I133">
-        <v>4.9141037338872442</v>
+        <v>4.914103733887244</v>
       </c>
       <c r="J133">
-        <v>1.1312082011969604</v>
+        <v>0.5656041005984802</v>
       </c>
       <c r="K133" t="s">
         <v>438</v>
@@ -7603,10 +7570,10 @@
         <v>63</v>
       </c>
       <c r="N133">
-        <v>10.333395702099351</v>
-      </c>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
+        <v>10.33339570209935</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14">
       <c r="A134">
         <v>2243</v>
       </c>
@@ -7626,16 +7593,16 @@
         <v>31</v>
       </c>
       <c r="G134">
-        <v>1.3166666666666671</v>
+        <v>1.316666666666667</v>
       </c>
       <c r="H134">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I134">
-        <v>1.8394899974443091</v>
+        <v>1.839489997444309</v>
       </c>
       <c r="J134">
-        <v>0.84688736087495997</v>
+        <v>0.21172184021874</v>
       </c>
       <c r="K134" t="s">
         <v>439</v>
@@ -7647,10 +7614,10 @@
         <v>64</v>
       </c>
       <c r="N134">
-        <v>20.956215160757949</v>
-      </c>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
+        <v>20.95621516075795</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14">
       <c r="A135">
         <v>2244</v>
       </c>
@@ -7670,16 +7637,16 @@
         <v>31</v>
       </c>
       <c r="G135">
-        <v>2.3166666666666669</v>
+        <v>2.316666666666667</v>
       </c>
       <c r="H135">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I135">
-        <v>1.3052766398051201</v>
+        <v>1.30527663980512</v>
       </c>
       <c r="J135">
-        <v>0.6009395485879836</v>
+        <v>0.1502348871469959</v>
       </c>
       <c r="K135" t="s">
         <v>440</v>
@@ -7691,10 +7658,10 @@
         <v>65</v>
       </c>
       <c r="N135">
-        <v>8.4514314807525732</v>
-      </c>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
+        <v>8.451431480752573</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14">
       <c r="A136">
         <v>2245</v>
       </c>
@@ -7714,16 +7681,16 @@
         <v>30</v>
       </c>
       <c r="G136">
-        <v>1.1833333333333329</v>
+        <v>1.183333333333333</v>
       </c>
       <c r="H136">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I136">
-        <v>1.9536410106373261</v>
+        <v>1.953641010637326</v>
       </c>
       <c r="J136">
-        <v>0.89944162887236678</v>
+        <v>0.2248604072180917</v>
       </c>
       <c r="K136" t="s">
         <v>441</v>
@@ -7738,7 +7705,7 @@
         <v>24.76446351512103</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:14">
       <c r="A137">
         <v>2246</v>
       </c>
@@ -7758,16 +7725,16 @@
         <v>29</v>
       </c>
       <c r="G137">
-        <v>4.3666666666666663</v>
+        <v>4.366666666666666</v>
       </c>
       <c r="H137">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I137">
-        <v>0.54592233772222543</v>
+        <v>0.5459223377222254</v>
       </c>
       <c r="J137">
-        <v>0.62834634664853839</v>
+        <v>0.06283463466485384</v>
       </c>
       <c r="K137" t="s">
         <v>442</v>
@@ -7779,10 +7746,10 @@
         <v>68</v>
       </c>
       <c r="N137">
-        <v>1.8753057402671871</v>
-      </c>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
+        <v>1.875305740267187</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14">
       <c r="A138">
         <v>2247</v>
       </c>
@@ -7805,13 +7772,13 @@
         <v>0.85</v>
       </c>
       <c r="H138">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I138">
         <v>1.207013953783036</v>
       </c>
       <c r="J138">
-        <v>1.389250367328396</v>
+        <v>0.1389250367328396</v>
       </c>
       <c r="K138" t="s">
         <v>443</v>
@@ -7823,10 +7790,10 @@
         <v>68</v>
       </c>
       <c r="N138">
-        <v>21.300246243230049</v>
-      </c>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
+        <v>21.30024624323005</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14">
       <c r="A139">
         <v>2248</v>
       </c>
@@ -7849,13 +7816,13 @@
         <v>0.75</v>
       </c>
       <c r="H139">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I139">
-        <v>1.1944699918528829</v>
+        <v>1.194469991852883</v>
       </c>
       <c r="J139">
-        <v>1.3748125029900429</v>
+        <v>0.1374812502990043</v>
       </c>
       <c r="K139" t="s">
         <v>444</v>
@@ -7870,7 +7837,7 @@
         <v>23.88939983705766</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:14">
       <c r="A140">
         <v>2250</v>
       </c>
@@ -7893,13 +7860,13 @@
         <v>12.21666666666667</v>
       </c>
       <c r="H140">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I140">
-        <v>0.66736085003529033</v>
+        <v>0.6673608500352903</v>
       </c>
       <c r="J140">
-        <v>0.76811979111450446</v>
+        <v>0.07681197911145045</v>
       </c>
       <c r="K140" t="s">
         <v>445</v>
@@ -7911,10 +7878,10 @@
         <v>79</v>
       </c>
       <c r="N140">
-        <v>0.81940622787416273</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
+        <v>0.8194062278741627</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14">
       <c r="A141">
         <v>2251</v>
       </c>
@@ -7937,13 +7904,13 @@
         <v>12.21666666666667</v>
       </c>
       <c r="H141">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I141">
-        <v>0.66736085003529033</v>
+        <v>0.6673608500352903</v>
       </c>
       <c r="J141">
-        <v>0.76811979111450446</v>
+        <v>0.07681197911145045</v>
       </c>
       <c r="K141" t="s">
         <v>446</v>
@@ -7955,10 +7922,10 @@
         <v>83</v>
       </c>
       <c r="N141">
-        <v>0.81940622787416273</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
+        <v>0.8194062278741627</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14">
       <c r="A142">
         <v>2252</v>
       </c>
@@ -7981,13 +7948,13 @@
         <v>12.08333333333333</v>
       </c>
       <c r="H142">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I142">
-        <v>0.66736085979707926</v>
+        <v>0.6673608597970793</v>
       </c>
       <c r="J142">
-        <v>0.76811980235013999</v>
+        <v>0.076811980235014</v>
       </c>
       <c r="K142" t="s">
         <v>447</v>
@@ -7999,10 +7966,10 @@
         <v>87</v>
       </c>
       <c r="N142">
-        <v>0.82844796388602948</v>
-      </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
+        <v>0.8284479638860295</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14">
       <c r="A143">
         <v>2253</v>
       </c>
@@ -8022,16 +7989,16 @@
         <v>22</v>
       </c>
       <c r="G143">
-        <v>12.266666666666669</v>
+        <v>12.26666666666667</v>
       </c>
       <c r="H143">
-        <v>8688.2392272041598</v>
+        <v>8688.23922720416</v>
       </c>
       <c r="I143">
-        <v>0.66736084646074068</v>
+        <v>0.6673608464607407</v>
       </c>
       <c r="J143">
-        <v>0.76811978700026495</v>
+        <v>0.0768119787000265</v>
       </c>
       <c r="K143" t="s">
         <v>448</v>
@@ -8043,7 +8010,7 @@
         <v>91</v>
       </c>
       <c r="N143">
-        <v>0.81606625246557962</v>
+        <v>0.8160662524655796</v>
       </c>
     </row>
   </sheetData>
